--- a/Dati/TabelleApp/app_2026_06.xlsx
+++ b/Dati/TabelleApp/app_2026_06.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="50">
   <si>
     <t xml:space="preserve">elenco spese per il periodo 1 giugno 2026 – 1 luglio 2026</t>
   </si>
@@ -45,30 +45,36 @@
     <t xml:space="preserve">Commento</t>
   </si>
   <si>
+    <t xml:space="preserve">Cibo Fuori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carburante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Spesa</t>
   </si>
   <si>
-    <t xml:space="preserve">Principale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">Autostrada</t>
   </si>
   <si>
-    <t xml:space="preserve">Cibo Fuori</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vestiti</t>
   </si>
   <si>
-    <t xml:space="preserve">Alcool</t>
-  </si>
-  <si>
     <t xml:space="preserve">Altro</t>
   </si>
   <si>
@@ -87,9 +93,6 @@
     <t xml:space="preserve">Tigotà</t>
   </si>
   <si>
-    <t xml:space="preserve">Bar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tabacco</t>
   </si>
   <si>
@@ -105,9 +108,6 @@
     <t xml:space="preserve">Pennabilli</t>
   </si>
   <si>
-    <t xml:space="preserve">Carburante</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bollette</t>
   </si>
   <si>
@@ -130,6 +130,12 @@
   </si>
   <si>
     <t xml:space="preserve">elenco entrate per il periodo 1 giugno 2026 – 1 luglio 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ripetizioni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco</t>
   </si>
   <si>
     <t xml:space="preserve">Stipendio</t>
@@ -441,7 +447,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>46199.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>10</v>
@@ -450,7 +456,7 @@
         <v>11</v>
       </c>
       <c r="D3" s="3">
-        <v>42.69</v>
+        <v>7.0</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>12</v>
@@ -470,7 +476,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>46199.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>14</v>
@@ -479,7 +485,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="3">
-        <v>1.6</v>
+        <v>7.0</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>12</v>
@@ -499,16 +505,16 @@
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>46198.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="3">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>12</v>
@@ -528,16 +534,16 @@
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>46197.0</v>
+        <v>46201.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="3">
-        <v>4.0</v>
+        <v>3.5</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>12</v>
@@ -557,16 +563,16 @@
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>46197.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="3">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>12</v>
@@ -586,7 +592,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>46196.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>15</v>
@@ -595,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="D8" s="3">
-        <v>4.5</v>
+        <v>49.74</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>12</v>
@@ -615,7 +621,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>46196.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>16</v>
@@ -624,7 +630,7 @@
         <v>11</v>
       </c>
       <c r="D9" s="3">
-        <v>25.0</v>
+        <v>1.6</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>12</v>
@@ -644,7 +650,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>46195.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>17</v>
@@ -653,7 +659,7 @@
         <v>11</v>
       </c>
       <c r="D10" s="3">
-        <v>1.5</v>
+        <v>42.69</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>12</v>
@@ -673,7 +679,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>46195.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>18</v>
@@ -682,7 +688,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="3">
-        <v>0.79</v>
+        <v>1.6</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>12</v>
@@ -697,21 +703,21 @@
         <v>13</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>46195.0</v>
+        <v>46198.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="3">
-        <v>17.45</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>12</v>
@@ -726,21 +732,21 @@
         <v>13</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>46195.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="3">
-        <v>3.5</v>
+        <v>4.0</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>12</v>
@@ -760,16 +766,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>46194.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="3">
-        <v>6.5</v>
+        <v>8.0</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>12</v>
@@ -789,16 +795,16 @@
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>46194.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>8.0</v>
+        <v>4.5</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>12</v>
@@ -818,16 +824,16 @@
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>46193.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="3">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>12</v>
@@ -842,21 +848,21 @@
         <v>13</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>46192.0</v>
+        <v>46195.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>6.0</v>
+        <v>1.5</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>12</v>
@@ -876,16 +882,16 @@
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>46192.0</v>
+        <v>46195.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="3">
-        <v>10.02</v>
+        <v>0.79</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>12</v>
@@ -900,21 +906,21 @@
         <v>13</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>46192.0</v>
+        <v>46195.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="3">
-        <v>0.5</v>
+        <v>17.45</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>12</v>
@@ -929,12 +935,12 @@
         <v>13</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>46191.0</v>
+        <v>46195.0</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>10</v>
@@ -943,7 +949,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="3">
-        <v>17.65</v>
+        <v>3.5</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>12</v>
@@ -963,16 +969,16 @@
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>46191.0</v>
+        <v>46194.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="3">
-        <v>5.0</v>
+        <v>6.5</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>12</v>
@@ -992,16 +998,16 @@
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>46190.0</v>
+        <v>46194.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="3">
-        <v>7.8</v>
+        <v>8.0</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>12</v>
@@ -1021,16 +1027,16 @@
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>46189.0</v>
+        <v>46193.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="3">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>12</v>
@@ -1045,21 +1051,21 @@
         <v>13</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v>46189.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="3">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>12</v>
@@ -1079,16 +1085,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>46189.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="3">
-        <v>50.0</v>
+        <v>10.02</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>12</v>
@@ -1103,21 +1109,21 @@
         <v>13</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>46189.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="3">
-        <v>15.0</v>
+        <v>0.5</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>12</v>
@@ -1132,21 +1138,21 @@
         <v>13</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D27" s="3">
-        <v>14.4</v>
+        <v>17.65</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>12</v>
@@ -1166,16 +1172,16 @@
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>46188.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D28" s="3">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>12</v>
@@ -1195,16 +1201,16 @@
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>46188.0</v>
+        <v>46190.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="3">
-        <v>5.83</v>
+        <v>7.8</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>12</v>
@@ -1224,16 +1230,16 @@
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>46187.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D30" s="3">
-        <v>4.6</v>
+        <v>7.0</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>12</v>
@@ -1253,16 +1259,16 @@
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>46185.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D31" s="3">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>12</v>
@@ -1277,21 +1283,21 @@
         <v>13</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>46184.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D32" s="3">
-        <v>82.2</v>
+        <v>50.0</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>12</v>
@@ -1311,16 +1317,16 @@
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>46184.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D33" s="3">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>12</v>
@@ -1335,12 +1341,12 @@
         <v>13</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>46183.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>10</v>
@@ -1349,7 +1355,7 @@
         <v>11</v>
       </c>
       <c r="D34" s="3">
-        <v>24.98</v>
+        <v>14.4</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>12</v>
@@ -1369,7 +1375,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <v>46183.0</v>
+        <v>46188.0</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>10</v>
@@ -1378,7 +1384,7 @@
         <v>11</v>
       </c>
       <c r="D35" s="3">
-        <v>14.96</v>
+        <v>13.0</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>12</v>
@@ -1398,16 +1404,16 @@
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <v>46183.0</v>
+        <v>46188.0</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D36" s="3">
-        <v>0.5</v>
+        <v>5.83</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>12</v>
@@ -1427,16 +1433,16 @@
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <v>46183.0</v>
+        <v>46187.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D37" s="3">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>12</v>
@@ -1456,16 +1462,16 @@
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>46183.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D38" s="3">
-        <v>2.5</v>
+        <v>20.0</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>12</v>
@@ -1480,12 +1486,12 @@
         <v>13</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>46182.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>15</v>
@@ -1494,7 +1500,7 @@
         <v>11</v>
       </c>
       <c r="D39" s="3">
-        <v>45.8</v>
+        <v>82.2</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>12</v>
@@ -1514,10 +1520,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>46182.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>11</v>
@@ -1543,16 +1549,16 @@
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D41" s="3">
-        <v>150.0</v>
+        <v>24.98</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>12</v>
@@ -1567,21 +1573,21 @@
         <v>13</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D42" s="3">
-        <v>70.0</v>
+        <v>14.96</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>12</v>
@@ -1596,21 +1602,21 @@
         <v>13</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D43" s="3">
-        <v>5.0</v>
+        <v>0.5</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>12</v>
@@ -1630,10 +1636,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <v>46181.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>11</v>
@@ -1659,16 +1665,16 @@
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>46179.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D45" s="3">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>12</v>
@@ -1683,21 +1689,21 @@
         <v>13</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>46179.0</v>
+        <v>46182.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D46" s="3">
-        <v>25.0</v>
+        <v>45.8</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>12</v>
@@ -1717,16 +1723,16 @@
     </row>
     <row r="47">
       <c r="A47" s="2">
-        <v>46179.0</v>
+        <v>46182.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D47" s="3">
-        <v>23.0</v>
+        <v>7.0</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>12</v>
@@ -1746,16 +1752,16 @@
     </row>
     <row r="48">
       <c r="A48" s="2">
-        <v>46178.0</v>
+        <v>46182.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D48" s="3">
-        <v>0.9</v>
+        <v>150.0</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>12</v>
@@ -1770,12 +1776,12 @@
         <v>13</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <v>46178.0</v>
+        <v>46182.0</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>33</v>
@@ -1784,7 +1790,7 @@
         <v>11</v>
       </c>
       <c r="D49" s="3">
-        <v>375.0</v>
+        <v>70.0</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>12</v>
@@ -1799,21 +1805,21 @@
         <v>13</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2">
-        <v>46178.0</v>
+        <v>46182.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D50" s="3">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>12</v>
@@ -1833,16 +1839,16 @@
     </row>
     <row r="51">
       <c r="A51" s="2">
-        <v>46177.0</v>
+        <v>46181.0</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D51" s="3">
-        <v>5.0</v>
+        <v>1.6</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>12</v>
@@ -1857,21 +1863,21 @@
         <v>13</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2">
-        <v>46177.0</v>
+        <v>46179.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D52" s="3">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>12</v>
@@ -1886,21 +1892,21 @@
         <v>13</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2">
-        <v>46176.0</v>
+        <v>46179.0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D53" s="3">
-        <v>1.6</v>
+        <v>25.0</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>12</v>
@@ -1920,16 +1926,16 @@
     </row>
     <row r="54">
       <c r="A54" s="2">
-        <v>46176.0</v>
+        <v>46179.0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D54" s="3">
-        <v>1.6</v>
+        <v>23.0</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>12</v>
@@ -1949,16 +1955,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2">
-        <v>46175.0</v>
+        <v>46178.0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D55" s="3">
-        <v>7.0</v>
+        <v>0.9</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>12</v>
@@ -1978,16 +1984,16 @@
     </row>
     <row r="56">
       <c r="A56" s="2">
-        <v>46175.0</v>
+        <v>46178.0</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D56" s="3">
-        <v>6.0</v>
+        <v>375.0</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>12</v>
@@ -2007,16 +2013,16 @@
     </row>
     <row r="57">
       <c r="A57" s="2">
-        <v>46174.0</v>
+        <v>46178.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D57" s="3">
-        <v>16.0</v>
+        <v>50.0</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>12</v>
@@ -2036,30 +2042,233 @@
     </row>
     <row r="58">
       <c r="A58" s="2">
+        <v>46177.0</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>46177.0</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>46176.0</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <v>46176.0</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2">
+        <v>46175.0</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <v>46175.0</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
         <v>46174.0</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D58" s="3">
+      <c r="B64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <v>46174.0</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="3">
         <v>1.6</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I58" s="1" t="s">
+      <c r="E65" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2114,7 +2323,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>46196.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>39</v>
@@ -2123,7 +2332,7 @@
         <v>11</v>
       </c>
       <c r="D3" s="3">
-        <v>1661.99</v>
+        <v>20.0</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>12</v>
@@ -2138,7 +2347,7 @@
         <v>13</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -2146,28 +2355,57 @@
         <v>46196.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="3">
+        <v>1661.99</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>46196.0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3">
         <v>1062.17</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>40</v>
+      <c r="E5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2187,7 +2425,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -2195,22 +2433,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>9</v>
